--- a/tables/datas/common/#PlayerAttr-玩家基础属性表.xlsx
+++ b/tables/datas/common/#PlayerAttr-玩家基础属性表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -598,6 +598,35 @@
         <v>5</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>mp_regen</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>每秒MP恢复量</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tables/datas/common/#PlayerAttr-玩家基础属性表.xlsx
+++ b/tables/datas/common/#PlayerAttr-玩家基础属性表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -618,15 +618,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>first_strike_haste</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>先攻加速（0~100，百分比）</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
